--- a/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
@@ -2368,7 +2368,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5056-1527-CM26</t>
+          <t>975-207-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2383,57 +2383,53 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>221607.75</v>
+        <v>1375.54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>975-207-CM26</t>
+          <t>2582-255-SE26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2448,7 +2444,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2458,12 +2454,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2473,28 +2469,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1375.54</v>
+        <v>218562.54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2582-255-SE26</t>
+          <t>2483-477-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>218562.54</v>
+        <v>175629.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2483-477-CM26</t>
+          <t>2343-337-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2574,22 +2574,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2599,32 +2599,28 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>175629.72</v>
+        <v>4226.17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2343-337-CM26</t>
+          <t>585-94-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2639,22 +2635,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2664,28 +2660,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4226.17</v>
+        <v>326243.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>585-94-CM26</t>
+          <t>867990-485-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2710,27 +2710,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>326243.38</v>
+        <v>224910</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1019-548-CM25</t>
+          <t>1020-32-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,17 +524,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4863.77</v>
+        <v>46181.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1019-549-CM25</t>
+          <t>633-132-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,27 +600,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>73666.52</v>
+        <v>23090.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>979-2016-CM25</t>
+          <t>1018-63-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>52865.75</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1020-454-CM25</t>
+          <t>2424-942-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,27 +722,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>245698.11</v>
+        <v>980179.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1020-461-CM25</t>
+          <t>2770-168-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.070.900-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE MAIPU</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>242159.1</v>
+        <v>407446.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5155-326-CM25</t>
+          <t>1020-197-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,42 +833,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>245470.34</v>
+        <v>1972.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2577-106-CM25</t>
+          <t>2216-394-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,32 +894,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -932,20 +932,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1057.32</v>
+        <v>116403.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1020-466-CM25</t>
+          <t>2366-4082-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,42 +959,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región de Arica y Parinacota</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +1004,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>39142.67</v>
+        <v>46532.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>976-420-CM25</t>
+          <t>867990-776-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,12 +1020,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,43 +1035,47 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6991.39</v>
+        <v>246330</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>633-1064-CM25</t>
+          <t>1415862-61-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,12 +1085,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1092,27 +1100,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1130,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>21867.23</v>
+        <v>15946</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>979-2352-CM25</t>
+          <t>1020-311-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1146,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1163,17 +1171,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1191,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>70870.64</v>
+        <v>414234.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2410-2648-CM25</t>
+          <t>980-225-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,32 +1207,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1237,24 +1245,20 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>151725</v>
+        <v>22587.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1415862-1-CM26</t>
+          <t>2446-1601-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1264,58 +1268,62 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Coquimbo </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>17197.88</v>
+        <v>806820</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2577-6-CM26</t>
+          <t>1347870-167-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1325,12 +1333,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1340,17 +1348,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región de Arica y Parinacota</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1370,13 +1378,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10780.36</v>
+        <v>29606.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1020-29-CM26</t>
+          <t>2366-4257-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,42 +1394,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región de Arica y Parinacota</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1431,13 +1439,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>46156.53</v>
+        <v>1268.85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>633-83-CM26</t>
+          <t>2585-4244-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1447,12 +1455,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1462,47 +1470,43 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región de Arica y Parinacota</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>565653.41</v>
+        <v>3172.12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1415862-13-CM26</t>
+          <t>2369-93-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1512,58 +1516,62 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región de Arica y Parinacota</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>70962.08</v>
+        <v>424116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1415862-12-CM26</t>
+          <t>1076403-37-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1573,12 +1581,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1588,43 +1596,47 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>69234.8</v>
+        <v>891357.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2410-54-CM26</t>
+          <t>1019-549-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1634,12 +1646,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1649,17 +1661,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1679,13 +1691,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>72770.88</v>
+        <v>73666.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>975-101-CM26</t>
+          <t>1019-548-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1695,17 +1707,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1725,12 +1737,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1740,13 +1752,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>224533.9</v>
+        <v>4863.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>975-102-CM26</t>
+          <t>2585-4439-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1756,42 +1768,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1801,13 +1813,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4470.83</v>
+        <v>29816.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1415862-20-CM26</t>
+          <t>979-2016-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1817,12 +1829,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1832,12 +1844,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1855,24 +1867,20 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>216159.22</v>
+        <v>52865.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2343-162-CM26</t>
+          <t>1020-454-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1882,12 +1890,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1897,12 +1905,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1912,28 +1920,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2536.13</v>
+        <v>245698.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1020-136-CM26</t>
+          <t>1020-461-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1943,12 +1955,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1973,12 +1985,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1988,13 +2000,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2579.15</v>
+        <v>242159.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1018-58-CM26</t>
+          <t>1020-466-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2004,12 +2016,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2034,12 +2046,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2049,13 +2061,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>55977.6</v>
+        <v>39142.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2483-191-CM26</t>
+          <t>976-420-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2065,27 +2077,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2095,12 +2107,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2110,13 +2122,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>61542.04</v>
+        <v>6991.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>976-81-CM26</t>
+          <t>633-1064-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2126,12 +2138,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2141,12 +2153,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2156,12 +2168,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2171,13 +2183,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>69725.08</v>
+        <v>21867.23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1020-162-CM26</t>
+          <t>979-2352-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2187,12 +2199,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2217,12 +2229,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2232,13 +2244,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>656393.34</v>
+        <v>70870.64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2793-487-CM26</t>
+          <t>1415862-1-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2248,27 +2260,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Instituto de Seguridad Laboral</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2278,32 +2290,28 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>402884.5</v>
+        <v>17197.88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2216-273-CM26</t>
+          <t>1020-29-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2313,12 +2321,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2343,32 +2351,28 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>104758.73</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>975-207-CM26</t>
+          <t>633-83-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2378,27 +2382,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2408,28 +2412,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1375.54</v>
+        <v>565653.41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2582-255-SE26</t>
+          <t>1415862-12-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2439,27 +2447,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>Instituto de Seguridad Laboral</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2477,24 +2485,20 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>218562.54</v>
+        <v>69234.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2483-477-CM26</t>
+          <t>1415862-13-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2504,27 +2508,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>Instituto de Seguridad Laboral</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2534,32 +2538,28 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>175629.72</v>
+        <v>70962.08</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2343-337-CM26</t>
+          <t>975-101-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2569,27 +2569,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4226.17</v>
+        <v>224533.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>585-94-CM26</t>
+          <t>975-102-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2660,90 +2660,708 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>326243.38</v>
+        <v>4470.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>1415862-20-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.533.000-0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Instituto de Seguridad Laboral</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>216159.22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1020-136-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>2579.15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1018-58-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>MSLI Latam Inc.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>55977.6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>976-81-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>69725.08</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1020-162-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>MSLI Latam Inc.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>656393.34</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2793-487-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.255.400-0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Iluste Municipalidad de Huechuraba</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>402884.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2216-273-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>104758.73</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2366-421-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>19992</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>975-207-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>1375.54</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2424-859-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.061.000-0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>887.03</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>867990-485-CM26</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>ago-2026</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>60.911.000-7</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
         <v>224910</v>
       </c>
     </row>

--- a/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="licencia-de-soft top org" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="licencia-de-soft top org" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2424-942-CM25</t>
+          <t>2410-120-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,47 +722,43 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>980179.2</v>
+        <v>70900.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2770-168-CM25</t>
+          <t>2424-942-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -772,58 +768,62 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.070.900-7</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAIPU</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>407446.96</v>
+        <v>980179.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1020-197-CM25</t>
+          <t>2770-168-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -848,27 +848,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.070.900-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE MAIPU</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1972.14</v>
+        <v>407446.96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2216-394-CM25</t>
+          <t>1020-197-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -914,42 +914,38 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MOP Dirección General de Concesiones</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>116403.66</v>
+        <v>1972.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2366-4082-CM25</t>
+          <t>2216-394-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -964,27 +960,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -997,20 +993,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>46532.33</v>
+        <v>116403.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>867990-776-CM25</t>
+          <t>2366-4082-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1035,47 +1035,43 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>246330</v>
+        <v>46532.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1415862-61-CM25</t>
+          <t>867990-776-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1085,12 +1081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1100,17 +1096,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1123,14 +1119,18 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>15946</v>
+        <v>246330</v>
       </c>
     </row>
     <row r="12">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1197,7 +1197,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>980-225-CM25</t>
+          <t>2408-4213-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1207,58 +1207,62 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>22587.39</v>
+        <v>136453.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2446-1601-CM25</t>
+          <t>2409-1257-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1273,7 +1277,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1283,47 +1287,43 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>806820</v>
+        <v>22193.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1347870-167-CM25</t>
+          <t>980-225-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1338,27 +1338,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>29606.49</v>
+        <v>22587.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2366-4257-CM25</t>
+          <t>2446-1601-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1394,58 +1394,62 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1268.85</v>
+        <v>806820</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2585-4244-CM25</t>
+          <t>1347870-167-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1455,12 +1459,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1480,7 +1484,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1500,13 +1504,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3172.12</v>
+        <v>29606.49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2369-93-CM25</t>
+          <t>2366-4257-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1521,12 +1525,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1541,37 +1545,33 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>424116</v>
+        <v>1268.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1076403-37-CM25</t>
+          <t>2408-4495-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1596,47 +1596,43 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>891357.6</v>
+        <v>1903.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1019-549-CM25</t>
+          <t>2585-4244-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1646,12 +1642,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1661,27 +1657,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1691,13 +1687,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>73666.52</v>
+        <v>3172.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1019-548-CM25</t>
+          <t>2369-93-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1707,58 +1703,62 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4863.77</v>
+        <v>424116</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2585-4439-CM25</t>
+          <t>1076403-37-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1783,43 +1783,47 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>29816.28</v>
+        <v>891357.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>979-2016-CM25</t>
+          <t>1019-549-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1834,7 +1838,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1859,12 +1863,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1874,13 +1878,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>52865.75</v>
+        <v>73666.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1020-454-CM25</t>
+          <t>1019-548-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1895,7 +1899,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1928,24 +1932,20 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>245698.11</v>
+        <v>4863.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1020-461-CM25</t>
+          <t>2585-4439-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1960,37 +1960,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2000,13 +2000,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>242159.1</v>
+        <v>29816.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1020-466-CM25</t>
+          <t>979-2016-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>39142.67</v>
+        <v>52865.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>976-420-CM25</t>
+          <t>1020-454-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2115,20 +2115,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6991.39</v>
+        <v>245698.11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>633-1064-CM25</t>
+          <t>1020-461-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2138,27 +2142,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2168,12 +2172,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2183,13 +2187,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>21867.23</v>
+        <v>242159.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>979-2352-CM25</t>
+          <t>1020-466-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2204,7 +2208,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2229,12 +2233,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2244,13 +2248,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>70870.64</v>
+        <v>39142.67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1415862-1-CM26</t>
+          <t>976-420-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2260,12 +2264,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2275,12 +2279,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2290,12 +2294,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2305,13 +2309,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>17197.88</v>
+        <v>6991.39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1020-29-CM26</t>
+          <t>633-1064-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2321,27 +2325,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2351,12 +2355,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2366,13 +2370,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>46156.53</v>
+        <v>21867.23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>633-83-CM26</t>
+          <t>979-2352-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2382,27 +2386,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2412,32 +2416,28 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>565653.41</v>
+        <v>70870.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1415862-12-CM26</t>
+          <t>2410-2648-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2462,43 +2462,47 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>69234.8</v>
+        <v>151725</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1415862-13-CM26</t>
+          <t>1020-29-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2508,27 +2512,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2553,13 +2557,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>70962.08</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>975-101-CM26</t>
+          <t>633-83-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2569,27 +2573,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2599,28 +2603,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>224533.9</v>
+        <v>565653.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>975-102-CM26</t>
+          <t>2410-54-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2635,37 +2643,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2675,13 +2683,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4470.83</v>
+        <v>72770.88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1415862-20-CM26</t>
+          <t>975-101-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2696,22 +2704,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2721,32 +2729,28 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>216159.22</v>
+        <v>224533.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1020-136-CM26</t>
+          <t>975-102-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2756,12 +2760,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2786,12 +2790,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2801,13 +2805,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2579.15</v>
+        <v>4470.83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1018-58-CM26</t>
+          <t>1020-136-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2822,7 +2826,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2847,12 +2851,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2862,13 +2866,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>55977.6</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>976-81-CM26</t>
+          <t>1018-58-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2883,12 +2887,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2908,12 +2912,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2923,13 +2927,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>69725.08</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1020-162-CM26</t>
+          <t>976-81-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2944,12 +2948,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2969,12 +2973,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2984,13 +2988,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>656393.34</v>
+        <v>69725.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2793-487-CM26</t>
+          <t>1020-162-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3005,7 +3009,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3015,12 +3019,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3030,32 +3034,28 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>402884.5</v>
+        <v>656393.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2216-273-CM26</t>
+          <t>2793-487-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>104758.73</v>
+        <v>402884.5</v>
       </c>
     </row>
     <row r="44">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">

--- a/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2410-120-CM25</t>
+          <t>4388-49-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,27 +722,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>70900.2</v>
+        <v>15440.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2424-942-CM25</t>
+          <t>2410-120-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,47 +783,43 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>980179.2</v>
+        <v>70900.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2770-168-CM25</t>
+          <t>2424-942-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,58 +829,62 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.070.900-7</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAIPU</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>407446.96</v>
+        <v>980179.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1020-197-CM25</t>
+          <t>894778-40-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -899,22 +899,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1972.14</v>
+        <v>47709.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2216-394-CM25</t>
+          <t>1020-197-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MOP Dirección General de Concesiones</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,32 +985,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>116403.66</v>
+        <v>1972.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2366-4082-CM25</t>
+          <t>4388-110-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1025,7 +1021,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1035,17 +1031,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1065,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>46532.33</v>
+        <v>11844.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>867990-776-CM25</t>
+          <t>2366-4082-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,7 +1082,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1096,47 +1092,43 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>246330</v>
+        <v>46532.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1020-311-CM25</t>
+          <t>867990-776-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1146,27 +1138,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1176,28 +1168,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>414234.24</v>
+        <v>246330</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2408-4213-CM25</t>
+          <t>734-761-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1222,27 +1218,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1256,13 +1252,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>136453.14</v>
+        <v>293475.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2409-1257-CM25</t>
+          <t>1020-311-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1272,12 +1268,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1287,27 +1283,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1317,13 +1313,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>22193.5</v>
+        <v>414234.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>980-225-CM25</t>
+          <t>2408-4213-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1333,58 +1329,62 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>22587.39</v>
+        <v>136453.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2446-1601-CM25</t>
+          <t>2409-1257-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1409,47 +1409,43 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>806820</v>
+        <v>22193.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1347870-167-CM25</t>
+          <t>980-225-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1464,27 +1460,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1504,13 +1500,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>29606.49</v>
+        <v>22587.39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2366-4257-CM25</t>
+          <t>2446-1601-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1520,58 +1516,62 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1268.85</v>
+        <v>806820</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2408-4495-CM25</t>
+          <t>1347870-167-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1596,17 +1596,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1903.27</v>
+        <v>29606.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2585-4244-CM25</t>
+          <t>2366-4257-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3172.12</v>
+        <v>1268.85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2369-93-CM25</t>
+          <t>2408-4495-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1708,57 +1708,53 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>424116</v>
+        <v>1903.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1076403-37-CM25</t>
+          <t>2585-4244-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1773,7 +1769,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1783,47 +1779,43 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>891357.6</v>
+        <v>3172.12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1019-549-CM25</t>
+          <t>2369-93-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1833,58 +1825,62 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>73666.52</v>
+        <v>424116</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1019-548-CM25</t>
+          <t>1076403-37-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1894,12 +1890,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1909,12 +1905,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1924,28 +1920,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4863.77</v>
+        <v>891357.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2585-4439-CM25</t>
+          <t>1019-549-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1970,27 +1970,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2000,13 +2000,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>29816.28</v>
+        <v>73666.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>979-2016-CM25</t>
+          <t>1019-548-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>52865.75</v>
+        <v>4863.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1020-454-CM25</t>
+          <t>2585-4439-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2092,17 +2092,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2115,24 +2115,20 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>245698.11</v>
+        <v>29816.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1020-461-CM25</t>
+          <t>979-2016-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2147,12 +2143,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2172,12 +2168,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2187,13 +2183,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>242159.1</v>
+        <v>52865.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1020-466-CM25</t>
+          <t>1020-454-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2203,17 +2199,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2233,28 +2229,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>39142.67</v>
+        <v>245698.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>976-420-CM25</t>
+          <t>1020-461-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6991.39</v>
+        <v>242159.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>633-1064-CM25</t>
+          <t>1020-466-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2330,22 +2330,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2370,13 +2370,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>21867.23</v>
+        <v>39142.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>979-2352-CM25</t>
+          <t>976-420-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2431,13 +2431,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>70870.64</v>
+        <v>6991.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2410-2648-CM25</t>
+          <t>633-1064-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2462,47 +2462,43 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>151725</v>
+        <v>21867.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1020-29-CM26</t>
+          <t>979-2352-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2512,12 +2508,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2542,12 +2538,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2557,13 +2553,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>46156.53</v>
+        <v>70870.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>633-83-CM26</t>
+          <t>2410-2648-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2573,12 +2569,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2588,27 +2584,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2622,13 +2618,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>565653.41</v>
+        <v>151725</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2410-54-CM26</t>
+          <t>1068038-145-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2638,12 +2634,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2653,27 +2649,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2683,13 +2679,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>72770.88</v>
+        <v>3804.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>975-101-CM26</t>
+          <t>1020-29-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2699,12 +2695,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2729,12 +2725,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2744,13 +2740,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>224533.9</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>975-102-CM26</t>
+          <t>633-83-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2760,27 +2756,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2790,28 +2786,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4470.83</v>
+        <v>565653.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1020-136-CM26</t>
+          <t>2410-54-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2821,42 +2821,42 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2579.15</v>
+        <v>72770.88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1018-58-CM26</t>
+          <t>975-101-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2882,12 +2882,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>55977.6</v>
+        <v>224533.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>976-81-CM26</t>
+          <t>975-102-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2943,17 +2943,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>69725.08</v>
+        <v>4470.83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1020-162-CM26</t>
+          <t>1020-136-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3049,13 +3049,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>656393.34</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2793-487-CM26</t>
+          <t>1018-58-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3095,32 +3095,28 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>402884.5</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2366-421-CM26</t>
+          <t>976-81-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3130,12 +3126,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3145,27 +3141,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3175,13 +3171,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>19992</v>
+        <v>69725.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>975-207-CM26</t>
+          <t>1020-162-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3191,12 +3187,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3221,12 +3217,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3236,13 +3232,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1375.54</v>
+        <v>656393.34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>894778-29-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3252,42 +3248,42 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3297,72 +3293,751 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>887.03</v>
+        <v>41174.95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>2366-421-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>19992</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>975-207-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>1375.54</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2424-859-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.061.000-0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>887.03</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1068038-18-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.511.000-2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1664.43</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1457902-17-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>60.501.000-8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>2641.09</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>867990-485-CM26</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>ago-2026</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>60.911.000-7</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
         <v>224910</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2408-851-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>42830.48</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2409-1109-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.170.101-8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>22175.65</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>734-655-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>293254.08</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>979-1248-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>28709.51</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>894778-42-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>60.501.000-8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>332367</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1020-317-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>39342.59</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1020-32-CM25</t>
+          <t>2369-7-SE25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,43 +539,47 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>96.899.890-0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>46181.52</v>
+        <v>413352.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>633-132-CM25</t>
+          <t>1020-32-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +594,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -623,20 +627,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>23090.76</v>
+        <v>46181.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1018-63-CM25</t>
+          <t>633-132-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +654,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,28 +684,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>55977.6</v>
+        <v>23090.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4388-49-CM25</t>
+          <t>633-141-SE25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +719,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +734,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,28 +749,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>15440.27</v>
+        <v>544960.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2410-120-CM25</t>
+          <t>858-98-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +784,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,43 +799,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>70900.2</v>
+        <v>10757.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2424-942-CM25</t>
+          <t>1018-63-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,62 +849,58 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>980179.2</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>894778-40-CM25</t>
+          <t>858-122-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,12 +910,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -909,12 +925,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,28 +940,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>47709.48</v>
+        <v>4482.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1020-197-CM25</t>
+          <t>2410-120-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,73 +975,77 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1972.14</v>
+        <v>70900.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4388-110-CM25</t>
+          <t>5056-960-SE25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,43 +1055,47 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>96.899.890-0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11844.59</v>
+        <v>688920.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2366-4082-CM25</t>
+          <t>2424-942-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,12 +1105,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1092,43 +1120,47 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>46532.33</v>
+        <v>980179.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>867990-776-CM25</t>
+          <t>1020-197-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,27 +1170,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1200,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1187,13 +1219,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>246330</v>
+        <v>1972.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>734-761-CM25</t>
+          <t>2366-4082-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1203,12 +1235,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1218,27 +1250,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1252,13 +1284,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>293475.42</v>
+        <v>46532.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1020-311-CM25</t>
+          <t>734-761-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1273,53 +1305,57 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>414234.24</v>
+        <v>293475.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2408-4213-CM25</t>
+          <t>1020-311-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1334,57 +1370,53 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>136453.14</v>
+        <v>414234.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2409-1257-CM25</t>
+          <t>2408-4213-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1394,22 +1426,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1424,28 +1456,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>22193.5</v>
+        <v>136453.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>980-225-CM25</t>
+          <t>2409-1257-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1460,7 +1496,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1470,43 +1506,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>22587.39</v>
+        <v>22193.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2446-1601-CM25</t>
+          <t>980-225-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1521,7 +1561,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1531,27 +1571,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1565,13 +1605,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>806820</v>
+        <v>22587.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1347870-167-CM25</t>
+          <t>2446-1601-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1586,53 +1626,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>29606.49</v>
+        <v>806820</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2366-4257-CM25</t>
+          <t>1347870-167-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1642,12 +1686,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1680,20 +1724,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1268.85</v>
+        <v>29606.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2408-4495-CM25</t>
+          <t>2366-4257-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1708,7 +1756,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1718,17 +1766,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1741,20 +1789,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1903.27</v>
+        <v>1268.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2585-4244-CM25</t>
+          <t>2408-4495-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1769,7 +1821,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1779,17 +1831,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1802,20 +1854,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3172.12</v>
+        <v>1903.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2369-93-CM25</t>
+          <t>2585-4244-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1830,12 +1886,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1855,12 +1911,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1874,13 +1930,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>424116</v>
+        <v>3172.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1076403-37-CM25</t>
+          <t>2369-93-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1900,22 +1956,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1939,13 +1995,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>891357.6</v>
+        <v>424116</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1019-549-CM25</t>
+          <t>1076403-37-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1955,12 +2011,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1970,12 +2026,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1985,28 +2041,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>73666.52</v>
+        <v>891357.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1019-548-CM25</t>
+          <t>1019-549-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2046,12 +2106,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2061,13 +2121,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4863.77</v>
+        <v>73666.52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2585-4439-CM25</t>
+          <t>1019-548-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2082,7 +2142,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2092,17 +2152,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2115,20 +2175,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>29816.28</v>
+        <v>4863.77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>979-2016-CM25</t>
+          <t>2585-4439-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2143,7 +2207,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2153,17 +2217,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2176,20 +2240,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>52865.75</v>
+        <v>29816.28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1020-454-CM25</t>
+          <t>979-2016-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2204,7 +2272,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2248,13 +2316,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>245698.11</v>
+        <v>52865.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1020-461-CM25</t>
+          <t>1020-454-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2269,12 +2337,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2294,28 +2362,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>242159.1</v>
+        <v>245698.11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1020-466-CM25</t>
+          <t>1020-461-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2325,12 +2397,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2355,12 +2427,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2370,13 +2442,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>39142.67</v>
+        <v>242159.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>976-420-CM25</t>
+          <t>1020-466-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2391,12 +2463,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2416,28 +2488,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6991.39</v>
+        <v>39142.67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>633-1064-CM25</t>
+          <t>976-420-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2452,7 +2528,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2462,12 +2538,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2477,28 +2553,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>21867.23</v>
+        <v>6991.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>979-2352-CM25</t>
+          <t>858-805-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2513,22 +2593,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2538,28 +2618,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>70870.64</v>
+        <v>5503.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2410-2648-CM25</t>
+          <t>633-1064-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2574,7 +2658,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2584,27 +2668,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2618,13 +2702,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>151725</v>
+        <v>21867.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1068038-145-CM25</t>
+          <t>858-808-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2639,7 +2723,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2649,12 +2733,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2672,20 +2756,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3804.83</v>
+        <v>75372.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1020-29-CM26</t>
+          <t>979-2352-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2695,12 +2783,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2725,28 +2813,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>46156.53</v>
+        <v>70870.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>633-83-CM26</t>
+          <t>2410-2648-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2756,12 +2848,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2771,27 +2863,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2805,13 +2897,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>565653.41</v>
+        <v>151725</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2410-54-CM26</t>
+          <t>1020-29-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2821,58 +2913,62 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>72770.88</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>975-101-CM26</t>
+          <t>633-83-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2882,27 +2978,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2912,28 +3008,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>224533.9</v>
+        <v>565653.41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>975-102-CM26</t>
+          <t>2410-54-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2948,37 +3048,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2988,13 +3088,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4470.83</v>
+        <v>72770.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1020-136-CM26</t>
+          <t>975-101-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3004,12 +3104,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3042,20 +3142,24 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2579.15</v>
+        <v>224533.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1018-58-CM26</t>
+          <t>975-102-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3065,12 +3169,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3095,12 +3199,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3110,13 +3214,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>55977.6</v>
+        <v>4470.83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>976-81-CM26</t>
+          <t>1020-136-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3131,12 +3235,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3156,28 +3260,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>69725.08</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1020-162-CM26</t>
+          <t>1018-58-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3192,7 +3300,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3232,13 +3340,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>656393.34</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>894778-29-CM26</t>
+          <t>976-81-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3248,12 +3356,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3263,12 +3371,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3286,20 +3394,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>41174.95</v>
+        <v>69725.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2366-421-CM26</t>
+          <t>1020-162-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3309,42 +3421,42 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3354,13 +3466,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>19992</v>
+        <v>656393.34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>975-207-CM26</t>
+          <t>5056-1527-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3375,53 +3487,57 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1375.54</v>
+        <v>221607.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>2366-421-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3436,37 +3552,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3476,13 +3592,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>887.03</v>
+        <v>19992</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1068038-18-CM26</t>
+          <t>975-207-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3497,7 +3613,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3507,12 +3623,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3530,20 +3646,24 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1664.43</v>
+        <v>1375.54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1457902-17-CM26</t>
+          <t>2424-859-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3558,53 +3678,57 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2641.09</v>
+        <v>887.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>867990-485-CM26</t>
+          <t>858-254-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3614,12 +3738,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3629,12 +3753,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3644,12 +3768,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,13 +3787,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>224910</v>
+        <v>4470.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2408-851-CM26</t>
+          <t>858-299-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3679,12 +3803,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3694,43 +3818,47 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>42830.48</v>
+        <v>24072.03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2409-1109-CM26</t>
+          <t>858-348-SE26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3740,32 +3868,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3778,20 +3906,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>22175.65</v>
+        <v>713286</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>734-655-CM26</t>
+          <t>2408-851-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3806,37 +3938,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3850,13 +3982,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>293254.08</v>
+        <v>42830.48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>979-1248-CM26</t>
+          <t>2409-1109-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3871,7 +4003,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3881,43 +4013,47 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>28709.51</v>
+        <v>22175.65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>894778-42-CM26</t>
+          <t>734-655-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3932,7 +4068,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3942,27 +4078,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3976,67 +4112,136 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>332367</v>
+        <v>293254.08</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>979-1248-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>28709.51</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>1020-317-CM26</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>61.202.000-0</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="n">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
         <v>39342.59</v>
       </c>
     </row>

--- a/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4245,6 +4245,71 @@
         <v>39342.59</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1020-334-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>1692.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
+++ b/docs/oc-top-organismos/licencia-de-software-de-ofimatica.xlsx
@@ -3683,7 +3683,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
